--- a/excel-template.xlsx
+++ b/excel-template.xlsx
@@ -8,9 +8,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수정2 시트" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'수정2 시트'!$A$1:$E$28</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>

--- a/excel-template.xlsx
+++ b/excel-template.xlsx
@@ -1967,7 +1967,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="64.5" customHeight="1" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="64.5" outlineLevelRow="0"/>
   <cols>
     <col width="56.66" customWidth="1" min="1" max="3"/>
     <col width="24.05" customWidth="1" min="2" max="2"/>
